--- a/OrganizedData/2025_organized/error_report.xlsx
+++ b/OrganizedData/2025_organized/error_report.xlsx
@@ -54,11 +54,17 @@
     <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c t="inlineStr" s="1">
         <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c t="inlineStr" s="1">
+        <is>
           <t>Day</t>
         </is>
       </c>
@@ -96,17 +102,142 @@
     <row r="2">
       <c t="inlineStr">
         <is>
+          <t>batch1</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>monday</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>monday_10448</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>MONDAY_10448</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>compression</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c t="n">
+        <v>0</v>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>MISSING - no data files for this test</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c t="inlineStr">
+        <is>
+          <t>batch1</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>monday</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>monday_10448</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>MONDAY_10448</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>tension</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c t="n">
+        <v>0</v>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>MISSING - no data files for this test</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c t="inlineStr">
+        <is>
+          <t>batch1</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>thursday</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>thursday_10435</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>THURSDAY_10435</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>tension</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c t="n">
+        <v>4</v>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>EXTRA 2 file(s) - check for duplicate runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c t="inlineStr">
+        <is>
+          <t>batch1</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
           <t>tuesday</t>
         </is>
       </c>
       <c t="inlineStr">
         <is>
-          <t>tuesday_10438</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>Tuesday 10438</t>
+          <t>tuesday_10454</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>Tuesday10454</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -120,28 +251,33 @@
         </is>
       </c>
       <c t="n">
-        <v>0</v>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>MISSING - no data files for this test</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c t="inlineStr">
-        <is>
-          <t>tuesday</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>tuesday_10438</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>Tuesday 10438</t>
+        <v>3</v>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>EXTRA 1 file(s) - check for duplicate runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c t="inlineStr">
+        <is>
+          <t>batch1</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>wensday</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>wensday_10453</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>WEDNESDAY_10453</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -155,28 +291,33 @@
         </is>
       </c>
       <c t="n">
-        <v>0</v>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>MISSING - no data files for this test</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c t="inlineStr">
-        <is>
-          <t>tuesday</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>tuesday_10438</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>Tuesday 10438</t>
+        <v>7</v>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>MISSING 1 file(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c t="inlineStr">
+        <is>
+          <t>batch2</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>thursday</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>thursday_10437</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>THURSDAY_10437</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -190,81 +331,11 @@
         </is>
       </c>
       <c t="n">
-        <v>0</v>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>MISSING - no data files for this test</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c t="inlineStr">
-        <is>
-          <t>tuesday</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>tuesday_10447</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>TUESDAY_10447</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>fracture</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c t="n">
-        <v>0</v>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>MISSING - no data files for this test</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c t="inlineStr">
-        <is>
-          <t>tuesday</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>tuesday_10454</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>Tuesday10454</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>fracture</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c t="n">
-        <v>0</v>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>MISSING - no data files for this test</t>
+        <v>3</v>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t>EXTRA 1 file(s) - check for duplicate runs</t>
         </is>
       </c>
     </row>
